--- a/input/16cut_hot.xlsx
+++ b/input/16cut_hot.xlsx
@@ -1804,6 +1804,36 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1811,30 +1841,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1843,11 +1849,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1858,11 +1864,38 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center" vertical="center"/>
@@ -1909,40 +1942,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="56">
@@ -1954,145 +1969,136 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="56">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
@@ -2101,73 +2107,67 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2627,7 +2627,7 @@
   <sheetData>
     <row r="1" hidden="1" ht="21" customHeight="1"/>
     <row r="2" ht="21" customHeight="1">
-      <c r="A2" s="307" t="inlineStr">
+      <c r="A2" s="303" t="inlineStr">
         <is>
           <t>16 граней горячая фиксация</t>
         </is>
@@ -2693,22 +2693,22 @@
           <t>CRYSTAL</t>
         </is>
       </c>
-      <c r="B4" s="303" t="inlineStr">
+      <c r="B4" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C4" s="311" t="n">
+      <c r="C4" s="313" t="n">
         <v>1440</v>
       </c>
       <c r="D4" s="133" t="n">
         <v>590</v>
       </c>
-      <c r="E4" s="311">
+      <c r="E4" s="313">
         <f>50+8</f>
         <v/>
       </c>
-      <c r="F4" s="311">
+      <c r="F4" s="313">
         <f>5+3+3</f>
         <v/>
       </c>
@@ -2721,7 +2721,7 @@
           <t>16cut/Crystal/SS6/Hot/001</t>
         </is>
       </c>
-      <c r="I4" s="314" t="inlineStr">
+      <c r="I4" s="302" t="inlineStr">
         <is>
           <t>001</t>
         </is>
@@ -2729,21 +2729,21 @@
     </row>
     <row r="5" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A5" s="428" t="n"/>
-      <c r="B5" s="301" t="inlineStr">
+      <c r="B5" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C5" s="301" t="n">
+      <c r="C5" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D5" s="134" t="n">
         <v>701</v>
       </c>
-      <c r="E5" s="301" t="n">
+      <c r="E5" s="311" t="n">
         <v>31</v>
       </c>
-      <c r="F5" s="301">
+      <c r="F5" s="311">
         <f>4+1</f>
         <v/>
       </c>
@@ -2760,21 +2760,21 @@
     </row>
     <row r="6" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A6" s="428" t="n"/>
-      <c r="B6" s="301" t="inlineStr">
+      <c r="B6" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C6" s="301" t="n">
+      <c r="C6" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D6" s="134" t="n">
         <v>755</v>
       </c>
-      <c r="E6" s="301" t="n">
+      <c r="E6" s="311" t="n">
         <v>18</v>
       </c>
-      <c r="F6" s="301" t="n">
+      <c r="F6" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="245">
@@ -2790,21 +2790,21 @@
     </row>
     <row r="7" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A7" s="428" t="n"/>
-      <c r="B7" s="318" t="inlineStr">
+      <c r="B7" s="320" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C7" s="318" t="n">
+      <c r="C7" s="320" t="n">
         <v>1440</v>
       </c>
       <c r="D7" s="138" t="n">
         <v>866</v>
       </c>
-      <c r="E7" s="318" t="n">
+      <c r="E7" s="320" t="n">
         <v>32</v>
       </c>
-      <c r="F7" s="318">
+      <c r="F7" s="320">
         <f>1+1+1</f>
         <v/>
       </c>
@@ -2832,10 +2832,10 @@
       <c r="D8" s="134" t="n">
         <v>866.1875</v>
       </c>
-      <c r="E8" s="312" t="n">
+      <c r="E8" s="314" t="n">
         <v>55</v>
       </c>
-      <c r="F8" s="312">
+      <c r="F8" s="314">
         <f>1+1</f>
         <v/>
       </c>
@@ -2863,10 +2863,10 @@
       <c r="D9" s="134" t="n">
         <v>1417.625</v>
       </c>
-      <c r="E9" s="312" t="n">
+      <c r="E9" s="314" t="n">
         <v>76</v>
       </c>
-      <c r="F9" s="312" t="n">
+      <c r="F9" s="314" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="264">
@@ -2893,10 +2893,10 @@
       <c r="D10" s="134" t="n">
         <v>866.1875</v>
       </c>
-      <c r="E10" s="312" t="n">
+      <c r="E10" s="314" t="n">
         <v>58</v>
       </c>
-      <c r="F10" s="312" t="n"/>
+      <c r="F10" s="314" t="n"/>
       <c r="G10" s="264">
         <f>E10-F10</f>
         <v/>
@@ -2921,10 +2921,10 @@
       <c r="D11" s="135" t="n">
         <v>1528.125</v>
       </c>
-      <c r="E11" s="313" t="n">
+      <c r="E11" s="315" t="n">
         <v>60</v>
       </c>
-      <c r="F11" s="313" t="n">
+      <c r="F11" s="315" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="265">
@@ -2939,26 +2939,26 @@
       <c r="I11" s="431" t="n"/>
     </row>
     <row r="12" ht="17.25" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A12" s="311" t="inlineStr">
+      <c r="A12" s="313" t="inlineStr">
         <is>
           <t>Crystal AB</t>
         </is>
       </c>
-      <c r="B12" s="303" t="inlineStr">
+      <c r="B12" s="310" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C12" s="303" t="n">
+      <c r="C12" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D12" s="133" t="n">
         <v>857</v>
       </c>
-      <c r="E12" s="303" t="n">
+      <c r="E12" s="310" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="303" t="n"/>
+      <c r="F12" s="310" t="n"/>
       <c r="G12" s="243">
         <f>E12-F12</f>
         <v/>
@@ -2968,7 +2968,7 @@
           <t>16cut/Сrystal AB/SS12/Hot/001+</t>
         </is>
       </c>
-      <c r="I12" s="315" t="inlineStr">
+      <c r="I12" s="301" t="inlineStr">
         <is>
           <t>001+</t>
         </is>
@@ -2976,21 +2976,21 @@
     </row>
     <row r="13" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A13" s="428" t="n"/>
-      <c r="B13" s="301" t="inlineStr">
+      <c r="B13" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C13" s="301" t="n">
+      <c r="C13" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D13" s="134" t="n">
         <v>845</v>
       </c>
-      <c r="E13" s="301" t="n">
+      <c r="E13" s="311" t="n">
         <v>16</v>
       </c>
-      <c r="F13" s="301" t="n"/>
+      <c r="F13" s="311" t="n"/>
       <c r="G13" s="245">
         <f>E13-F13</f>
         <v/>
@@ -3004,21 +3004,21 @@
     </row>
     <row r="14" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A14" s="428" t="n"/>
-      <c r="B14" s="301" t="inlineStr">
+      <c r="B14" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C14" s="301" t="n">
+      <c r="C14" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D14" s="134" t="n">
         <v>1113</v>
       </c>
-      <c r="E14" s="301" t="n">
+      <c r="E14" s="311" t="n">
         <v>11</v>
       </c>
-      <c r="F14" s="301" t="n"/>
+      <c r="F14" s="311" t="n"/>
       <c r="G14" s="245">
         <f>E14-F14</f>
         <v/>
@@ -3032,21 +3032,21 @@
     </row>
     <row r="15" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A15" s="432" t="n"/>
-      <c r="B15" s="302" t="inlineStr">
+      <c r="B15" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C15" s="302" t="n">
+      <c r="C15" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D15" s="135" t="n">
         <v>845</v>
       </c>
-      <c r="E15" s="302" t="n">
+      <c r="E15" s="312" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="302" t="n"/>
+      <c r="F15" s="312" t="n"/>
       <c r="G15" s="246">
         <f>E15-F15</f>
         <v/>
@@ -3064,21 +3064,21 @@
           <t>NEW AB</t>
         </is>
       </c>
-      <c r="B16" s="303" t="inlineStr">
+      <c r="B16" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C16" s="303" t="n">
+      <c r="C16" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D16" s="133" t="n">
         <v>855</v>
       </c>
-      <c r="E16" s="303" t="n">
+      <c r="E16" s="310" t="n">
         <v>110</v>
       </c>
-      <c r="F16" s="303">
+      <c r="F16" s="310">
         <f>1+3+1+2</f>
         <v/>
       </c>
@@ -3091,7 +3091,7 @@
           <t>16cut/New AB/SS6/Hot/112</t>
         </is>
       </c>
-      <c r="I16" s="315" t="inlineStr">
+      <c r="I16" s="301" t="inlineStr">
         <is>
           <t>112</t>
         </is>
@@ -3099,21 +3099,21 @@
     </row>
     <row r="17" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A17" s="428" t="n"/>
-      <c r="B17" s="301" t="inlineStr">
+      <c r="B17" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C17" s="301" t="n">
+      <c r="C17" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D17" s="134" t="n">
         <v>1076</v>
       </c>
-      <c r="E17" s="301" t="n">
+      <c r="E17" s="311" t="n">
         <v>117</v>
       </c>
-      <c r="F17" s="301">
+      <c r="F17" s="311">
         <f>1+1</f>
         <v/>
       </c>
@@ -3130,21 +3130,21 @@
     </row>
     <row r="18" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A18" s="428" t="n"/>
-      <c r="B18" s="301" t="inlineStr">
+      <c r="B18" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C18" s="301" t="n">
+      <c r="C18" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D18" s="134" t="n">
         <v>1076</v>
       </c>
-      <c r="E18" s="301" t="n">
+      <c r="E18" s="311" t="n">
         <v>105</v>
       </c>
-      <c r="F18" s="301">
+      <c r="F18" s="311">
         <f>1+1+1</f>
         <v/>
       </c>
@@ -3161,21 +3161,21 @@
     </row>
     <row r="19" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A19" s="428" t="n"/>
-      <c r="B19" s="336" t="inlineStr">
+      <c r="B19" s="330" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C19" s="301" t="n">
+      <c r="C19" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D19" s="134" t="n">
         <v>1296</v>
       </c>
-      <c r="E19" s="301" t="n">
+      <c r="E19" s="311" t="n">
         <v>204</v>
       </c>
-      <c r="F19" s="301">
+      <c r="F19" s="311">
         <f>1+1+1</f>
         <v/>
       </c>
@@ -3192,21 +3192,21 @@
     </row>
     <row r="20" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A20" s="428" t="n"/>
-      <c r="B20" s="336" t="inlineStr">
+      <c r="B20" s="330" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C20" s="301" t="n">
+      <c r="C20" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D20" s="134" t="n">
         <v>1241</v>
       </c>
-      <c r="E20" s="301" t="n">
+      <c r="E20" s="311" t="n">
         <v>196</v>
       </c>
-      <c r="F20" s="301">
+      <c r="F20" s="311">
         <f>1+1+1+1+1+1</f>
         <v/>
       </c>
@@ -3223,21 +3223,21 @@
     </row>
     <row r="21" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A21" s="428" t="n"/>
-      <c r="B21" s="336" t="inlineStr">
+      <c r="B21" s="330" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C21" s="301" t="n">
+      <c r="C21" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D21" s="134" t="n">
         <v>1793</v>
       </c>
-      <c r="E21" s="301" t="n">
+      <c r="E21" s="311" t="n">
         <v>197</v>
       </c>
-      <c r="F21" s="301">
+      <c r="F21" s="311">
         <f>1+1+1+1+1+1</f>
         <v/>
       </c>
@@ -3254,21 +3254,21 @@
     </row>
     <row r="22" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A22" s="428" t="n"/>
-      <c r="B22" s="336" t="inlineStr">
+      <c r="B22" s="330" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C22" s="301" t="n">
+      <c r="C22" s="311" t="n">
         <v>288</v>
       </c>
       <c r="D22" s="134" t="n">
         <v>1241</v>
       </c>
-      <c r="E22" s="301" t="n">
+      <c r="E22" s="311" t="n">
         <v>174</v>
       </c>
-      <c r="F22" s="301">
+      <c r="F22" s="311">
         <f>5+1+1</f>
         <v/>
       </c>
@@ -3285,21 +3285,21 @@
     </row>
     <row r="23" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A23" s="428" t="n"/>
-      <c r="B23" s="336" t="inlineStr">
+      <c r="B23" s="330" t="inlineStr">
         <is>
           <t>SS34</t>
         </is>
       </c>
-      <c r="C23" s="301" t="n">
+      <c r="C23" s="311" t="n">
         <v>144</v>
       </c>
       <c r="D23" s="134" t="n">
         <v>1572</v>
       </c>
-      <c r="E23" s="301" t="n">
+      <c r="E23" s="311" t="n">
         <v>128</v>
       </c>
-      <c r="F23" s="301" t="n"/>
+      <c r="F23" s="311" t="n"/>
       <c r="G23" s="245">
         <f>E23-F23</f>
         <v/>
@@ -3313,21 +3313,21 @@
     </row>
     <row r="24" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A24" s="430" t="n"/>
-      <c r="B24" s="339" t="inlineStr">
+      <c r="B24" s="331" t="inlineStr">
         <is>
           <t>SS40</t>
         </is>
       </c>
-      <c r="C24" s="302" t="n">
+      <c r="C24" s="312" t="n">
         <v>144</v>
       </c>
       <c r="D24" s="135" t="n">
         <v>1572</v>
       </c>
-      <c r="E24" s="302" t="n">
+      <c r="E24" s="312" t="n">
         <v>97</v>
       </c>
-      <c r="F24" s="302" t="n">
+      <c r="F24" s="312" t="n">
         <v>5</v>
       </c>
       <c r="G24" s="246">
@@ -3342,26 +3342,26 @@
       <c r="I24" s="431" t="n"/>
     </row>
     <row r="25" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A25" s="303" t="inlineStr">
+      <c r="A25" s="310" t="inlineStr">
         <is>
           <t>JET BLACK</t>
         </is>
       </c>
-      <c r="B25" s="303" t="inlineStr">
+      <c r="B25" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C25" s="303" t="n">
+      <c r="C25" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D25" s="133" t="n">
         <v>1113.75</v>
       </c>
-      <c r="E25" s="303" t="n">
+      <c r="E25" s="310" t="n">
         <v>59</v>
       </c>
-      <c r="F25" s="303" t="n">
+      <c r="F25" s="310" t="n">
         <v>2</v>
       </c>
       <c r="G25" s="243">
@@ -3373,7 +3373,7 @@
           <t>16cut/Jet Black/SS16/Hot/002</t>
         </is>
       </c>
-      <c r="I25" s="315" t="inlineStr">
+      <c r="I25" s="301" t="inlineStr">
         <is>
           <t>002</t>
         </is>
@@ -3381,21 +3381,21 @@
     </row>
     <row r="26" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A26" s="428" t="n"/>
-      <c r="B26" s="301" t="inlineStr">
+      <c r="B26" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C26" s="301" t="n">
+      <c r="C26" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D26" s="134" t="n">
         <v>1638.625</v>
       </c>
-      <c r="E26" s="301" t="n">
+      <c r="E26" s="311" t="n">
         <v>59</v>
       </c>
-      <c r="F26" s="301" t="n"/>
+      <c r="F26" s="311" t="n"/>
       <c r="G26" s="245">
         <f>E26-F26</f>
         <v/>
@@ -3409,21 +3409,21 @@
     </row>
     <row r="27" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A27" s="432" t="n"/>
-      <c r="B27" s="302" t="inlineStr">
+      <c r="B27" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C27" s="302" t="n">
+      <c r="C27" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D27" s="135" t="n">
         <v>1113.75</v>
       </c>
-      <c r="E27" s="302" t="n">
+      <c r="E27" s="312" t="n">
         <v>60</v>
       </c>
-      <c r="F27" s="302" t="n"/>
+      <c r="F27" s="312" t="n"/>
       <c r="G27" s="246">
         <f>E27-F27</f>
         <v/>
@@ -3441,21 +3441,21 @@
           <t>Lt. Colorado Topaz</t>
         </is>
       </c>
-      <c r="B28" s="303" t="inlineStr">
+      <c r="B28" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C28" s="303" t="n">
+      <c r="C28" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D28" s="133" t="n">
         <v>1169</v>
       </c>
-      <c r="E28" s="303" t="n">
+      <c r="E28" s="310" t="n">
         <v>20</v>
       </c>
-      <c r="F28" s="303" t="n"/>
+      <c r="F28" s="310" t="n"/>
       <c r="G28" s="243">
         <f>E28-F28</f>
         <v/>
@@ -3465,7 +3465,7 @@
           <t>16cut/Lt.Colorado Topaz/SS16/Hot/010</t>
         </is>
       </c>
-      <c r="I28" s="315" t="inlineStr">
+      <c r="I28" s="301" t="inlineStr">
         <is>
           <t>010</t>
         </is>
@@ -3473,21 +3473,21 @@
     </row>
     <row r="29" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A29" s="428" t="n"/>
-      <c r="B29" s="301" t="inlineStr">
+      <c r="B29" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C29" s="301" t="n">
+      <c r="C29" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D29" s="134" t="n">
         <v>1749</v>
       </c>
-      <c r="E29" s="301" t="n">
+      <c r="E29" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F29" s="301" t="n"/>
+      <c r="F29" s="311" t="n"/>
       <c r="G29" s="245">
         <f>E29-F29</f>
         <v/>
@@ -3501,21 +3501,21 @@
     </row>
     <row r="30" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A30" s="430" t="n"/>
-      <c r="B30" s="302" t="inlineStr">
+      <c r="B30" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C30" s="302" t="n">
+      <c r="C30" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D30" s="135" t="n">
         <v>1169</v>
       </c>
-      <c r="E30" s="302" t="n">
+      <c r="E30" s="312" t="n">
         <v>20</v>
       </c>
-      <c r="F30" s="302" t="n"/>
+      <c r="F30" s="312" t="n"/>
       <c r="G30" s="246">
         <f>E30-F30</f>
         <v/>
@@ -3544,10 +3544,10 @@
       <c r="D31" s="133" t="n">
         <v>1169</v>
       </c>
-      <c r="E31" s="303" t="n">
+      <c r="E31" s="310" t="n">
         <v>20</v>
       </c>
-      <c r="F31" s="303">
+      <c r="F31" s="310">
         <f>2+2</f>
         <v/>
       </c>
@@ -3560,7 +3560,7 @@
           <t>16cut/Lt.Sapphire/SS16/Hot/011</t>
         </is>
       </c>
-      <c r="I31" s="315" t="inlineStr">
+      <c r="I31" s="301" t="inlineStr">
         <is>
           <t>011</t>
         </is>
@@ -3579,10 +3579,10 @@
       <c r="D32" s="134" t="n">
         <v>1749.125</v>
       </c>
-      <c r="E32" s="301" t="n">
+      <c r="E32" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F32" s="301" t="n">
+      <c r="F32" s="311" t="n">
         <v>2</v>
       </c>
       <c r="G32" s="245">
@@ -3609,10 +3609,10 @@
       <c r="D33" s="135" t="n">
         <v>1169</v>
       </c>
-      <c r="E33" s="302" t="n">
+      <c r="E33" s="312" t="n">
         <v>20</v>
       </c>
-      <c r="F33" s="302" t="n">
+      <c r="F33" s="312" t="n">
         <v>2</v>
       </c>
       <c r="G33" s="246">
@@ -3632,21 +3632,21 @@
           <t>SAPPHIRE</t>
         </is>
       </c>
-      <c r="B34" s="301" t="inlineStr">
+      <c r="B34" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C34" s="301" t="n">
+      <c r="C34" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D34" s="134" t="n">
         <v>1749.125</v>
       </c>
-      <c r="E34" s="301" t="n">
+      <c r="E34" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F34" s="301">
+      <c r="F34" s="311">
         <f>1+2</f>
         <v/>
       </c>
@@ -3659,7 +3659,7 @@
           <t>16cut/Sapphire/SS20/Hot/013</t>
         </is>
       </c>
-      <c r="I34" s="315" t="inlineStr">
+      <c r="I34" s="301" t="inlineStr">
         <is>
           <t>013</t>
         </is>
@@ -3682,10 +3682,10 @@
       <c r="D35" s="133" t="n">
         <v>1169</v>
       </c>
-      <c r="E35" s="303" t="n">
+      <c r="E35" s="310" t="n">
         <v>20</v>
       </c>
-      <c r="F35" s="303" t="n">
+      <c r="F35" s="310" t="n">
         <v>2</v>
       </c>
       <c r="G35" s="243">
@@ -3697,7 +3697,7 @@
           <t>16cut/Aquamarine/SS16/Hot/016</t>
         </is>
       </c>
-      <c r="I35" s="315" t="inlineStr">
+      <c r="I35" s="301" t="inlineStr">
         <is>
           <t>016</t>
         </is>
@@ -3716,10 +3716,10 @@
       <c r="D36" s="134" t="n">
         <v>1749.125</v>
       </c>
-      <c r="E36" s="301" t="n">
+      <c r="E36" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F36" s="301" t="n">
+      <c r="F36" s="311" t="n">
         <v>2</v>
       </c>
       <c r="G36" s="245">
@@ -3746,10 +3746,10 @@
       <c r="D37" s="135" t="n">
         <v>1169</v>
       </c>
-      <c r="E37" s="302" t="n">
+      <c r="E37" s="312" t="n">
         <v>20</v>
       </c>
-      <c r="F37" s="302" t="n">
+      <c r="F37" s="312" t="n">
         <v>2</v>
       </c>
       <c r="G37" s="246">
@@ -3780,10 +3780,10 @@
       <c r="D38" s="133" t="n">
         <v>1169</v>
       </c>
-      <c r="E38" s="303" t="n">
+      <c r="E38" s="310" t="n">
         <v>20</v>
       </c>
-      <c r="F38" s="303" t="n"/>
+      <c r="F38" s="310" t="n"/>
       <c r="G38" s="243">
         <f>E38-F38</f>
         <v/>
@@ -3793,7 +3793,7 @@
           <t>16cut/Indicolite/SS16/Hot/014</t>
         </is>
       </c>
-      <c r="I38" s="315" t="inlineStr">
+      <c r="I38" s="301" t="inlineStr">
         <is>
           <t>014</t>
         </is>
@@ -3812,10 +3812,10 @@
       <c r="D39" s="134" t="n">
         <v>1749.125</v>
       </c>
-      <c r="E39" s="301" t="n">
+      <c r="E39" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F39" s="301" t="n"/>
+      <c r="F39" s="311" t="n"/>
       <c r="G39" s="245">
         <f>E39-F39</f>
         <v/>
@@ -3840,10 +3840,10 @@
       <c r="D40" s="135" t="n">
         <v>1169</v>
       </c>
-      <c r="E40" s="302" t="n">
+      <c r="E40" s="312" t="n">
         <v>20</v>
       </c>
-      <c r="F40" s="302" t="n"/>
+      <c r="F40" s="312" t="n"/>
       <c r="G40" s="246">
         <f>E40-F40</f>
         <v/>
@@ -3861,21 +3861,21 @@
           <t>CAPRI BLUE</t>
         </is>
       </c>
-      <c r="B41" s="303" t="inlineStr">
+      <c r="B41" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C41" s="303" t="n">
+      <c r="C41" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D41" s="133" t="n">
         <v>1169</v>
       </c>
-      <c r="E41" s="303" t="n">
+      <c r="E41" s="310" t="n">
         <v>20</v>
       </c>
-      <c r="F41" s="303" t="n"/>
+      <c r="F41" s="310" t="n"/>
       <c r="G41" s="243">
         <f>E41-F41</f>
         <v/>
@@ -3885,7 +3885,7 @@
           <t>16cut/Capri Blue/SS16/Hot/017</t>
         </is>
       </c>
-      <c r="I41" s="315" t="inlineStr">
+      <c r="I41" s="301" t="inlineStr">
         <is>
           <t>017</t>
         </is>
@@ -3893,21 +3893,21 @@
     </row>
     <row r="42" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A42" s="428" t="n"/>
-      <c r="B42" s="301" t="inlineStr">
+      <c r="B42" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C42" s="301" t="n">
+      <c r="C42" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D42" s="134" t="n">
         <v>1749.125</v>
       </c>
-      <c r="E42" s="301" t="n">
+      <c r="E42" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F42" s="301" t="n"/>
+      <c r="F42" s="311" t="n"/>
       <c r="G42" s="245">
         <f>E42-F42</f>
         <v/>
@@ -3921,21 +3921,21 @@
     </row>
     <row r="43" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A43" s="430" t="n"/>
-      <c r="B43" s="302" t="inlineStr">
+      <c r="B43" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C43" s="302" t="n">
+      <c r="C43" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D43" s="135" t="n">
         <v>1169</v>
       </c>
-      <c r="E43" s="302" t="n">
+      <c r="E43" s="312" t="n">
         <v>20</v>
       </c>
-      <c r="F43" s="302" t="n"/>
+      <c r="F43" s="312" t="n"/>
       <c r="G43" s="246">
         <f>E43-F43</f>
         <v/>
@@ -3948,26 +3948,26 @@
       <c r="I43" s="431" t="n"/>
     </row>
     <row r="44" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A44" s="303" t="inlineStr">
+      <c r="A44" s="310" t="inlineStr">
         <is>
           <t>MONTANA</t>
         </is>
       </c>
-      <c r="B44" s="303" t="inlineStr">
+      <c r="B44" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C44" s="303" t="n">
+      <c r="C44" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D44" s="133" t="n">
         <v>1169</v>
       </c>
-      <c r="E44" s="303" t="n">
+      <c r="E44" s="310" t="n">
         <v>20</v>
       </c>
-      <c r="F44" s="303">
+      <c r="F44" s="310">
         <f>2+2</f>
         <v/>
       </c>
@@ -3980,7 +3980,7 @@
           <t>16cut/Montana/SS16/Hot/018</t>
         </is>
       </c>
-      <c r="I44" s="315" t="inlineStr">
+      <c r="I44" s="301" t="inlineStr">
         <is>
           <t>018</t>
         </is>
@@ -3988,21 +3988,21 @@
     </row>
     <row r="45" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A45" s="428" t="n"/>
-      <c r="B45" s="301" t="inlineStr">
+      <c r="B45" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C45" s="301" t="n">
+      <c r="C45" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D45" s="134" t="n">
         <v>1749.125</v>
       </c>
-      <c r="E45" s="301" t="n">
+      <c r="E45" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F45" s="301" t="n">
+      <c r="F45" s="311" t="n">
         <v>2</v>
       </c>
       <c r="G45" s="245">
@@ -4018,21 +4018,21 @@
     </row>
     <row r="46" ht="17.25" customHeight="1" thickBot="1" thickTop="1">
       <c r="A46" s="432" t="n"/>
-      <c r="B46" s="302" t="inlineStr">
+      <c r="B46" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C46" s="302" t="n">
+      <c r="C46" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D46" s="135" t="n">
         <v>1169</v>
       </c>
-      <c r="E46" s="302" t="n">
+      <c r="E46" s="312" t="n">
         <v>20</v>
       </c>
-      <c r="F46" s="302" t="n">
+      <c r="F46" s="312" t="n">
         <v>2</v>
       </c>
       <c r="G46" s="246">
@@ -4047,26 +4047,26 @@
       <c r="I46" s="431" t="n"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A47" s="303" t="inlineStr">
+      <c r="A47" s="310" t="inlineStr">
         <is>
           <t>Lt. Peridot</t>
         </is>
       </c>
-      <c r="B47" s="303" t="inlineStr">
+      <c r="B47" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C47" s="303" t="n">
+      <c r="C47" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D47" s="133" t="n">
         <v>1169</v>
       </c>
-      <c r="E47" s="303" t="n">
+      <c r="E47" s="310" t="n">
         <v>20</v>
       </c>
-      <c r="F47" s="303" t="n"/>
+      <c r="F47" s="310" t="n"/>
       <c r="G47" s="242">
         <f>E47-F47</f>
         <v/>
@@ -4076,7 +4076,7 @@
           <t>16cut/Lt. Peridot/SS16/Hot/024</t>
         </is>
       </c>
-      <c r="I47" s="315" t="inlineStr">
+      <c r="I47" s="301" t="inlineStr">
         <is>
           <t>024</t>
         </is>
@@ -4084,21 +4084,21 @@
     </row>
     <row r="48" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A48" s="428" t="n"/>
-      <c r="B48" s="301" t="inlineStr">
+      <c r="B48" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C48" s="301" t="n">
+      <c r="C48" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D48" s="134" t="n">
         <v>1749</v>
       </c>
-      <c r="E48" s="301" t="n">
+      <c r="E48" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F48" s="301" t="n"/>
+      <c r="F48" s="311" t="n"/>
       <c r="G48" s="247">
         <f>E48-F48</f>
         <v/>
@@ -4112,21 +4112,21 @@
     </row>
     <row r="49" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A49" s="432" t="n"/>
-      <c r="B49" s="302" t="inlineStr">
+      <c r="B49" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C49" s="302" t="n">
+      <c r="C49" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D49" s="135" t="n">
         <v>1169</v>
       </c>
-      <c r="E49" s="302" t="n">
+      <c r="E49" s="312" t="n">
         <v>20</v>
       </c>
-      <c r="F49" s="302" t="n"/>
+      <c r="F49" s="312" t="n"/>
       <c r="G49" s="247">
         <f>E49-F49</f>
         <v/>
@@ -4139,26 +4139,26 @@
       <c r="I49" s="431" t="n"/>
     </row>
     <row r="50" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A50" s="301" t="inlineStr">
+      <c r="A50" s="311" t="inlineStr">
         <is>
           <t>OLIVINE</t>
         </is>
       </c>
-      <c r="B50" s="333" t="inlineStr">
+      <c r="B50" s="344" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C50" s="333" t="n">
+      <c r="C50" s="344" t="n">
         <v>1440</v>
       </c>
       <c r="D50" s="134" t="n">
         <v>1749.125</v>
       </c>
-      <c r="E50" s="301" t="n">
+      <c r="E50" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F50" s="301" t="n"/>
+      <c r="F50" s="311" t="n"/>
       <c r="G50" s="256">
         <f>E50-F50</f>
         <v/>
@@ -4168,7 +4168,7 @@
           <t>16cut/Olivine/SS20/Hot/027</t>
         </is>
       </c>
-      <c r="I50" s="315" t="inlineStr">
+      <c r="I50" s="301" t="inlineStr">
         <is>
           <t>027</t>
         </is>
@@ -4180,21 +4180,21 @@
           <t>HYACINTH</t>
         </is>
       </c>
-      <c r="B51" s="303" t="inlineStr">
+      <c r="B51" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C51" s="303" t="n">
+      <c r="C51" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D51" s="133" t="n">
         <v>1224</v>
       </c>
-      <c r="E51" s="303" t="n">
+      <c r="E51" s="310" t="n">
         <v>20</v>
       </c>
-      <c r="F51" s="303" t="n"/>
+      <c r="F51" s="310" t="n"/>
       <c r="G51" s="243">
         <f>E51-F51</f>
         <v/>
@@ -4204,7 +4204,7 @@
           <t>16cut/Hyacinth/SS16/Hot/031</t>
         </is>
       </c>
-      <c r="I51" s="315" t="inlineStr">
+      <c r="I51" s="301" t="inlineStr">
         <is>
           <t>031</t>
         </is>
@@ -4212,21 +4212,21 @@
     </row>
     <row r="52" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A52" s="428" t="n"/>
-      <c r="B52" s="301" t="inlineStr">
+      <c r="B52" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C52" s="301" t="n">
+      <c r="C52" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D52" s="134" t="n">
         <v>1803</v>
       </c>
-      <c r="E52" s="301" t="n">
+      <c r="E52" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F52" s="301" t="n"/>
+      <c r="F52" s="311" t="n"/>
       <c r="G52" s="245">
         <f>E52-F52</f>
         <v/>
@@ -4240,21 +4240,21 @@
     </row>
     <row r="53" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A53" s="430" t="n"/>
-      <c r="B53" s="302" t="inlineStr">
+      <c r="B53" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C53" s="302" t="n">
+      <c r="C53" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D53" s="135" t="n">
         <v>1224</v>
       </c>
-      <c r="E53" s="302" t="n">
+      <c r="E53" s="312" t="n">
         <v>20</v>
       </c>
-      <c r="F53" s="302" t="n"/>
+      <c r="F53" s="312" t="n"/>
       <c r="G53" s="245">
         <f>E53-F53</f>
         <v/>
@@ -4267,23 +4267,23 @@
       <c r="I53" s="431" t="n"/>
     </row>
     <row r="54" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A54" s="303" t="inlineStr">
+      <c r="A54" s="310" t="inlineStr">
         <is>
           <t>Lt. Siam</t>
         </is>
       </c>
-      <c r="B54" s="303" t="inlineStr">
+      <c r="B54" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C54" s="303" t="n">
+      <c r="C54" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D54" s="133" t="n">
         <v>1224.25</v>
       </c>
-      <c r="E54" s="303" t="n">
+      <c r="E54" s="310" t="n">
         <v>39</v>
       </c>
       <c r="F54" s="32" t="n">
@@ -4298,7 +4298,7 @@
           <t>16cut/Lt.Siam/SS16/Hot/033</t>
         </is>
       </c>
-      <c r="I54" s="315" t="inlineStr">
+      <c r="I54" s="301" t="inlineStr">
         <is>
           <t>033</t>
         </is>
@@ -4306,18 +4306,18 @@
     </row>
     <row r="55" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A55" s="428" t="n"/>
-      <c r="B55" s="318" t="inlineStr">
+      <c r="B55" s="320" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C55" s="318" t="n">
+      <c r="C55" s="320" t="n">
         <v>1440</v>
       </c>
       <c r="D55" s="138" t="n">
         <v>1803.3125</v>
       </c>
-      <c r="E55" s="318" t="n">
+      <c r="E55" s="320" t="n">
         <v>39</v>
       </c>
       <c r="F55" s="84" t="n"/>
@@ -4334,18 +4334,18 @@
     </row>
     <row r="56" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A56" s="432" t="n"/>
-      <c r="B56" s="302" t="inlineStr">
+      <c r="B56" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C56" s="302" t="n">
+      <c r="C56" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D56" s="135" t="n">
         <v>1224</v>
       </c>
-      <c r="E56" s="302" t="n">
+      <c r="E56" s="312" t="n">
         <v>40</v>
       </c>
       <c r="F56" s="33" t="n"/>
@@ -4377,7 +4377,7 @@
       <c r="D57" s="133" t="n">
         <v>1224.25</v>
       </c>
-      <c r="E57" s="303" t="n">
+      <c r="E57" s="310" t="n">
         <v>20</v>
       </c>
       <c r="F57" s="32" t="n">
@@ -4392,7 +4392,7 @@
           <t>16cut/Garnet/SS16/Hot/034</t>
         </is>
       </c>
-      <c r="I57" s="315" t="inlineStr">
+      <c r="I57" s="301" t="inlineStr">
         <is>
           <t>034</t>
         </is>
@@ -4411,7 +4411,7 @@
       <c r="D58" s="134" t="n">
         <v>1803.3125</v>
       </c>
-      <c r="E58" s="301" t="n">
+      <c r="E58" s="311" t="n">
         <v>20</v>
       </c>
       <c r="F58" s="34" t="n"/>
@@ -4439,7 +4439,7 @@
       <c r="D59" s="135" t="n">
         <v>1224.25</v>
       </c>
-      <c r="E59" s="302" t="n">
+      <c r="E59" s="312" t="n">
         <v>20</v>
       </c>
       <c r="F59" s="33" t="n"/>
@@ -4455,23 +4455,23 @@
       <c r="I59" s="431" t="n"/>
     </row>
     <row r="60" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A60" s="301" t="inlineStr">
+      <c r="A60" s="311" t="inlineStr">
         <is>
           <t>CITRINE</t>
         </is>
       </c>
-      <c r="B60" s="301" t="inlineStr">
+      <c r="B60" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C60" s="301" t="n">
+      <c r="C60" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D60" s="134" t="n">
         <v>1803.3125</v>
       </c>
-      <c r="E60" s="301" t="n">
+      <c r="E60" s="311" t="n">
         <v>20</v>
       </c>
       <c r="F60" s="34" t="n"/>
@@ -4484,7 +4484,7 @@
           <t>16cut/Citrine/SS20/Hot/035</t>
         </is>
       </c>
-      <c r="I60" s="315" t="inlineStr">
+      <c r="I60" s="301" t="inlineStr">
         <is>
           <t>035</t>
         </is>
@@ -4492,18 +4492,18 @@
     </row>
     <row r="61" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A61" s="432" t="n"/>
-      <c r="B61" s="302" t="inlineStr">
+      <c r="B61" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C61" s="302" t="n">
+      <c r="C61" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D61" s="135" t="n">
         <v>1224.25</v>
       </c>
-      <c r="E61" s="302" t="n">
+      <c r="E61" s="312" t="n">
         <v>20</v>
       </c>
       <c r="F61" s="33" t="n"/>
@@ -4548,7 +4548,7 @@
           <t>16cut/Golden Shadow/SS20/Hot/052</t>
         </is>
       </c>
-      <c r="I62" s="347" t="inlineStr">
+      <c r="I62" s="321" t="inlineStr">
         <is>
           <t>052</t>
         </is>
@@ -4571,11 +4571,11 @@
     <mergeCell ref="A57:A59"/>
     <mergeCell ref="A60:A61"/>
     <mergeCell ref="I51:I53"/>
+    <mergeCell ref="A47:A49"/>
     <mergeCell ref="I38:I40"/>
-    <mergeCell ref="A47:A49"/>
     <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A44:A46"/>
     <mergeCell ref="I35:I37"/>
-    <mergeCell ref="A44:A46"/>
     <mergeCell ref="A35:A37"/>
     <mergeCell ref="I44:I46"/>
     <mergeCell ref="I31:I33"/>
@@ -4594,8 +4594,8 @@
     <mergeCell ref="I25:I27"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="I28:I30"/>
+    <mergeCell ref="A2:D2"/>
     <mergeCell ref="I16:I24"/>
-    <mergeCell ref="A2:D2"/>
     <mergeCell ref="A16:A24"/>
   </mergeCells>
   <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.3149606299212598" footer="0.3149606299212598"/>
